--- a/script/梅长苏_脉动回来_完整视频脚本.xlsx
+++ b/script/梅长苏_脉动回来_完整视频脚本.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>脉动（达能）。三集各讲一个官方卖点：三重维生素 / 三连电解质 / 清爽果味。款式（普通款 or 脉动+电解质）待确认。</t>
+          <t>脉动（达能）。三集各讲一个官方卖点：三重维生素 / 三连电解质 / 清爽果味。款式已确认：普通款脉动（青柠、水蜜桃、橙子蓝标瓶）。</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>植入的款式（普通款 / 脉动+电解质）待确认，见“脉动卖点核对”。</t>
+          <t>植入款式已确认：普通款脉动（青柠、水蜜桃、橙子蓝标瓶），见“脉动卖点核对”。</t>
         </is>
       </c>
       <c r="C41" s="7" t="n"/>
@@ -2701,8 +2701,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>手机屏幕：“投诉不成立，扣款撤销。顾客账号已被限制。”
-字幕：“伤势几乎痊愈，只差最后一口气。”</t>
+          <t>手机屏幕：“投诉不成立，扣款撤销。顾客账号已被限制。”</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
@@ -2715,9 +2714,9 @@
           <t>近景</t>
         </is>
       </c>
-      <c r="J11" s="13" t="inlineStr">
-        <is>
-          <t>字幕为 t160 原文；与镜头9“3/3”表述接近，成片时可统一为“只差最后一口气”【待确认】</t>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>成片未使用该字幕。</t>
         </is>
       </c>
     </row>
@@ -3073,14 +3072,14 @@
       <c r="F7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>产品款式</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>普通款脉动 vs 脉动+电解质（含椰子水、5种电解质，是独立的运动饮料产品）</t>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>普通款脉动（青柠、水蜜桃、橙子蓝标瓶）</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -3093,14 +3092,14 @@
           <t>达能中国官网 · 脉动品牌页</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>待确认：植入哪一款</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>目前脚本按普通款写；若改为“脉动+电解质”，需改第2集卖点台词</t>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>已确认：普通款脉动</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>三集卖点沿用普通款 3D源动力口径：三重维生素 / 三连电解质 / 清爽果味</t>
         </is>
       </c>
     </row>
